--- a/artfynd/A 61374-2025 artfynd.xlsx
+++ b/artfynd/A 61374-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108911504</v>
+        <v>1976527</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnmyra skjutbaneparkering, Upl</t>
+          <t>Kvarnmyra, 200 m S om skjutbanan  (232), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667138.7338167157</v>
+        <v>667066</v>
       </c>
       <c r="R2" t="n">
-        <v>6642866.891519792</v>
+        <v>6642731</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-01-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-01-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +759,491 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>ek</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109363878</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kvarnmyra, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>667116</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6642857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Anlagd gräsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Asken står i en anlagd gräsmatta vid ett hus som verkar användas av de som frekventerar skjutbanorna.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Thorleif Joelson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114335475</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83314</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6471</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gulvit blekspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sclerophora pallida</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kvarnmyra, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>667096</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6642843</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vårdträd vid gården, på ask</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>83320514</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kvarnmyra, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>667111</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6642859</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>80D51087-1D1C-46B8-AFBE-80CD66DDB0DA</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2004-11-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2004-11-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niina Sallmén, Nina Söderström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108911504</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvarnmyra skjutbaneparkering, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>667139</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6642867</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
